--- a/5/search/FY3_Missile3_results/fine_tuned/comparison.xlsx
+++ b/5/search/FY3_Missile3_results/fine_tuned/comparison.xlsx
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>81.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>119.9</v>
+        <v>125.4</v>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F3" t="n">
-        <v>2.900000000000002</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/5/search/FY3_Missile3_results/fine_tuned/comparison.xlsx
+++ b/5/search/FY3_Missile3_results/fine_tuned/comparison.xlsx
@@ -470,10 +470,10 @@
         <v>81</v>
       </c>
       <c r="C2" t="n">
-        <v>120.4</v>
+        <v>102</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="C3" t="n">
-        <v>125.4</v>
+        <v>135.4</v>
       </c>
       <c r="D3" t="n">
-        <v>22.8</v>
+        <v>19.6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>3.100000000000001</v>
       </c>
     </row>
   </sheetData>
